--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A21D70C-683D-4DFC-9806-ACF5CA8EDC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E14E16D-243A-45D0-8FD6-C86ABE2D58D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3246,6 +3246,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B147" t="s">
+        <v>91</v>
+      </c>
+      <c r="C147" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" s="5">
+        <v>775</v>
+      </c>
+      <c r="E147">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E14E16D-243A-45D0-8FD6-C86ABE2D58D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7EEE3D-7521-45B7-AE29-B9154F0AC4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="710" windowWidth="19230" windowHeight="11290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3263,6 +3263,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B148" t="s">
+        <v>35</v>
+      </c>
+      <c r="C148" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" s="5">
+        <v>675</v>
+      </c>
+      <c r="E148">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7EEE3D-7521-45B7-AE29-B9154F0AC4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0F246B-AA27-4DA4-90F3-536743B35732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="710" windowWidth="19230" windowHeight="11290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3280,6 +3280,40 @@
         <v>9</v>
       </c>
     </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B149" t="s">
+        <v>36</v>
+      </c>
+      <c r="C149" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" s="5">
+        <v>700</v>
+      </c>
+      <c r="E149">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B150" t="s">
+        <v>38</v>
+      </c>
+      <c r="C150" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="5">
+        <v>725</v>
+      </c>
+      <c r="E150">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0F246B-AA27-4DA4-90F3-536743B35732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D18D1FB-950B-40A5-AD2F-82480E100B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3282,16 +3282,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
-        <v>46315</v>
+        <v>46293</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C149" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D149" s="5">
-        <v>700</v>
+        <v>-5375</v>
       </c>
       <c r="E149">
         <v>9</v>
@@ -3302,15 +3302,32 @@
         <v>46315</v>
       </c>
       <c r="B150" t="s">
+        <v>36</v>
+      </c>
+      <c r="C150" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="5">
+        <v>700</v>
+      </c>
+      <c r="E150">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B151" t="s">
         <v>38</v>
       </c>
-      <c r="C150" t="s">
-        <v>6</v>
-      </c>
-      <c r="D150" s="5">
+      <c r="C151" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" s="5">
         <v>725</v>
       </c>
-      <c r="E150">
+      <c r="E151">
         <v>9</v>
       </c>
     </row>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D18D1FB-950B-40A5-AD2F-82480E100B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE57C38-F9F2-457E-8DFD-254B5D06D47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -749,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3331,6 +3331,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B152" t="s">
+        <v>40</v>
+      </c>
+      <c r="C152" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="5">
+        <v>750</v>
+      </c>
+      <c r="E152">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
